--- a/codelijst-template.xlsx
+++ b/codelijst-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vandenbrouckekristof/Documents/uncapped/digitaal_vlaanderen/OSLO-codelijsten-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CAE19E-89FC-4D4B-B22A-E323FBEFF0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC3933-C9AD-F745-B078-DBD5B1B8A410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="codelijst" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>@id</t>
   </si>
@@ -47,6 +47,24 @@
   </si>
   <si>
     <t>notation</t>
+  </si>
+  <si>
+    <t>https://example.org/id/concept/SchemeA/Concept1</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#Concept</t>
+  </si>
+  <si>
+    <t>Concept 1</t>
+  </si>
+  <si>
+    <t>First concept in Scheme A</t>
+  </si>
+  <si>
+    <t>https://example.org/id/conceptscheme/SchemeA</t>
+  </si>
+  <si>
+    <t>C1</t>
   </si>
 </sst>
 </file>
@@ -209,7 +227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="42.6640625" customWidth="1"/>
@@ -243,6 +261,29 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -255,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC371A-FD4C-EB44-8C96-587FE309B299}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -281,6 +322,29 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/codelijst-template.xlsx
+++ b/codelijst-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr dateCompatibility="0" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vandenbrouckekristof/Documents/uncapped/digitaal_vlaanderen/OSLO-codelijsten-generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vandenbrouckekristof/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C97E823E-FCF3-804E-853E-11243B62A23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{18C41E7E-9A2A-3C4A-BDF2-B9EF52651849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16600" tabRatio="752" activeTab="2" xr2:uid="{7CDDD550-6CF8-4D93-8060-C83373E5608E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="25" uniqueCount="21">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="29" uniqueCount="23">
   <si>
     <t>@id</t>
   </si>
@@ -220,9 +220,6 @@
     </r>
   </si>
   <si>
-    <t>Een opmerking over deze codelijst</t>
-  </si>
-  <si>
     <t>Ontwerp Standaard</t>
   </si>
   <si>
@@ -236,13 +233,22 @@
   </si>
   <si>
     <t>OntwerpStandaard</t>
+  </si>
+  <si>
+    <t>StandaardStatus</t>
+  </si>
+  <si>
+    <t>Informatie over de status van het document</t>
+  </si>
+  <si>
+    <t>Standaard Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,12 +323,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF585858"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -374,21 +374,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -398,11 +394,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -416,6 +412,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -522,13 +519,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15373" name="Button 13">
+        <xdr:cNvPr id="17421" name="Button 13">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s14349"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E32463F9-4185-5EA3-68CB-F7F558B46C2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37491B92-8B60-902A-16EE-E0BBE12BFF32}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -908,255 +905,255 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="7" customWidth="1"/>
-    <col min="2" max="9" width="9.1640625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="2.83203125" style="7" customWidth="1"/>
-    <col min="11" max="16384" width="9.1640625" style="7" hidden="1"/>
+    <col min="1" max="1" width="3.33203125" style="5" customWidth="1"/>
+    <col min="2" max="9" width="9.1640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="2.83203125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9.1640625" style="5" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:10" ht="37" x14ac:dyDescent="0.45">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="17" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="11"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2"/>
@@ -1182,7 +1179,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <controls>
-    <control shapeId="15373" r:id="rId3" name="Button 13">
+    <control shapeId="17421" r:id="rId3" name="Button 13">
       <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ExportSheetsToCSV">
         <anchor moveWithCells="1">
           <from>
@@ -1227,7 +1224,7 @@
         <f>_xlfn.CONCAT(_BEHEER!$E$23,"id/concept/")</f>
         <v>https://data.vlaanderen.be/id/concept/</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1236,7 +1233,7 @@
         <f>_xlfn.CONCAT(_BEHEER!$E$23,"id/conceptscheme/")</f>
         <v>https://data.vlaanderen.be/id/conceptscheme/</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1249,100 +1246,131 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C62971-3A1C-4127-8731-E44715BBA9AB}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="67" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="5" customWidth="1"/>
-    <col min="4" max="4" width="20.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="48.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1640625" style="4" hidden="1"/>
+    <col min="1" max="1" width="67" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="48.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="0" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="19" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:9" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="A3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="D3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="D4" s="6"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels " error="Definities beginnen steeds met een hoofdletter en eindigen met een punt. Er mogen geen speciale karakters gebruikt worden." sqref="E4:E1048576" xr:uid="{97C59B91-CCBB-4637-85D1-6B417F2EFD70}">
-      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(E4,ROW(INDIRECT("1:"&amp;LEN(E4))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ .'"))), RIGHT(E4,1)=".", EXACT(LEFT(E4,1),UPPER(LEFT(E4,1))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels " error="Definities beginnen steeds met een hoofdletter en eindigen met een punt. Er mogen geen speciale karakters gebruikt worden." sqref="E6:E1048576" xr:uid="{97C59B91-CCBB-4637-85D1-6B417F2EFD70}">
+      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(E6,ROW(INDIRECT("1:"&amp;LEN(E6))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ .'"))), RIGHT(E6,1)=".", EXACT(LEFT(E6,1),UPPER(LEFT(E6,1))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="Labels beginnen steeds met een hoofdletter en eindigen zonder punt. Er mogen geen speciale karakters gebruikt worden." sqref="D1048576" xr:uid="{1F74FF6B-CD93-4494-AD3A-D3DC5CD071DD}">
-      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(D1048576,ROW(INDIRECT("1:"&amp;LEN(D1048576))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ "))), NOT(RIGHT(D1048576,1)="."), EXACT(LEFT(D1048576,1),UPPER(LEFT(D1048576,1))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="Labels beginnen steeds met een hoofdletter en eindigen zonder punt. Er mogen geen speciale karakters gebruikt worden." sqref="D1048575:D1048576" xr:uid="{1F74FF6B-CD93-4494-AD3A-D3DC5CD071DD}">
+      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(D1048575,ROW(INDIRECT("1:"&amp;LEN(D1048575))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ "))), NOT(RIGHT(D1048575,1)="."), EXACT(LEFT(D1048575,1),UPPER(LEFT(D1048575,1))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{E3E3AA12-7DF6-4C02-949D-45EA6F099383}">
-      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(C4,ROW(INDIRECT("1:"&amp;LEN(C4))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ-"))), EXACT(LEFT(C4,1),UPPER(LEFT(C4,1))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C1048576 C2" xr:uid="{E3E3AA12-7DF6-4C02-949D-45EA6F099383}">
+      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(C2,ROW(INDIRECT("1:"&amp;LEN(C2))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ-"))), EXACT(LEFT(C2,1),UPPER(LEFT(C2,1))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="Labels beginnen steeds met een hoofdletter en eindigen zonder punt. Er mogen geen speciale karakters gebruikt worden." sqref="D2 D4:D1048575" xr:uid="{79D89D22-1736-4C2E-BA40-0C10AED95402}">
-      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(D2,ROW(INDIRECT("1:"&amp;LEN(D2))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ-/()ö "))), NOT(RIGHT(D2,1)="."), EXACT(LEFT(D2,1),UPPER(LEFT(D2,1))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="Labels beginnen steeds met een hoofdletter en eindigen zonder punt. Er mogen geen speciale karakters gebruikt worden." sqref="D1 D6:D1048574" xr:uid="{79D89D22-1736-4C2E-BA40-0C10AED95402}">
+      <formula1>AND(ISNUMBER(SUMPRODUCT(SEARCH(MID(D1,ROW(INDIRECT("1:"&amp;LEN(D1))),1),"0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ-/()ö "))), NOT(RIGHT(D1,1)="."), EXACT(LEFT(D1,1),UPPER(LEFT(D1,1))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{909F89CB-BC6F-2746-8408-BBABCE1DEE2A}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{1DF2FEB7-AD28-4147-B17E-5F2EF07A0335}"/>
-    <hyperlink ref="G3" r:id="rId3" xr:uid="{FFC30395-9A48-BE4F-BE34-AC876B38C9B2}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{44F496D3-2669-054F-A5C6-6571F600D24B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1350,15 +1378,15 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="@id moet altijd beginnen met de basis URI en een geldige URI zijn. Concepten moeten na de basis URI /id/concept/ bevatten en Conceptschemes /id/conceptscheme/ zoals aangegeven in de Vlaamse URI standaard." xr:uid="{DAAFA6B5-F89F-40B1-B8D2-AA3B2CC72257}">
           <x14:formula1>
-            <xm:f>OR(LEFT(A4,LEN(_VALIDATIE!$A$2))=_VALIDATIE!$A$2,LEFT(A4,LEN(_VALIDATIE!$A$3))=_VALIDATIE!$A$3)</xm:f>
+            <xm:f>OR(LEFT(A3,LEN(_VALIDATIE!$A$2))=_VALIDATIE!$A$2,LEFT(A3,LEN(_VALIDATIE!$A$3))=_VALIDATIE!$A$3)</xm:f>
           </x14:formula1>
-          <xm:sqref>F4:H1048576 A4:A1048576</xm:sqref>
+          <xm:sqref>A6:A1048576 H5:H1048576 F6:G1048576 H3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vormregels" error="@type moet steeds een URI bevatten W3C's SKOS Core: Concept of Conceptscheme. Kies deze uit het dropdown menu in de cel." xr:uid="{9CE40068-9012-4421-B80D-5E42FE8A4E46}">
           <x14:formula1>
             <xm:f>_VALIDATIE!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B4:B1048576</xm:sqref>
+          <xm:sqref>B6:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
